--- a/docs/quality/golden-reports/tenant-payment-status-xlsx.xlsx
+++ b/docs/quality/golden-reports/tenant-payment-status-xlsx.xlsx
@@ -7,10 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Tenants Payments Status Report" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Tenants Payment's Status Report" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Tenants Payments Status Report'!$A$5:$J$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Tenants Payment''s Status Report'!$A$5:$J$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -497,7 +497,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tenants Payments Status Report</t>
+          <t>Tenants Payment's Status Report</t>
         </is>
       </c>
     </row>
@@ -511,7 +511,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Prepared by admin · Generated 14 Aug 2026 10:35</t>
+          <t>Prepared by admin · Generated 14 Aug 2026 16:41</t>
         </is>
       </c>
     </row>
